--- a/Piaui/2026/Julho/ResultadosTRI_2EM_MT/Simulado_III/ResumoTheta_2EM_MT_S3.xlsx
+++ b/Piaui/2026/Julho/ResultadosTRI_2EM_MT/Simulado_III/ResumoTheta_2EM_MT_S3.xlsx
@@ -389,7 +389,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>308.655368275466</v>
+        <v>309.44353458989</v>
       </c>
     </row>
     <row r="3">
@@ -397,7 +397,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>51.6678871361539</v>
+        <v>51.2883041905143</v>
       </c>
     </row>
     <row r="4">
@@ -405,7 +405,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="n">
-        <v>16.7396690440977</v>
+        <v>16.5743660660054</v>
       </c>
     </row>
     <row r="5">
@@ -413,7 +413,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="n">
-        <v>228.412018389905</v>
+        <v>230.67382110056</v>
       </c>
     </row>
     <row r="6">
@@ -421,7 +421,7 @@
         <v>6</v>
       </c>
       <c r="B6" t="n">
-        <v>265.49341878551</v>
+        <v>266.657670876034</v>
       </c>
     </row>
     <row r="7">
@@ -429,7 +429,7 @@
         <v>7</v>
       </c>
       <c r="B7" t="n">
-        <v>301.118590193984</v>
+        <v>301.866715208456</v>
       </c>
     </row>
     <row r="8">
@@ -437,7 +437,7 @@
         <v>8</v>
       </c>
       <c r="B8" t="n">
-        <v>347.106109718019</v>
+        <v>347.569007748552</v>
       </c>
     </row>
     <row r="9">
@@ -445,7 +445,7 @@
         <v>9</v>
       </c>
       <c r="B9" t="n">
-        <v>478.568318540094</v>
+        <v>483.496918576413</v>
       </c>
     </row>
     <row r="10">
@@ -453,7 +453,7 @@
         <v>10</v>
       </c>
       <c r="B10" t="n">
-        <v>0.465103719715603</v>
+        <v>0.471941472716726</v>
       </c>
     </row>
     <row r="11">
@@ -461,7 +461,7 @@
         <v>11</v>
       </c>
       <c r="B11" t="n">
-        <v>2.29630146414747</v>
+        <v>2.30582920513906</v>
       </c>
     </row>
   </sheetData>
